--- a/src/main/resources/static/templateImport/Template_Upload_User.xlsx
+++ b/src/main/resources/static/templateImport/Template_Upload_User.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\QUANBUIVUMINH\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ECM-GIT\ecm-api\src\main\resources\static\templateImport\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0874EDC5-DBA1-4D20-8DB8-BF27A5BD336F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C235E7BD-017B-4B07-8866-E880C6E0A8E6}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t>(1)</t>
   </si>
@@ -125,6 +125,36 @@
   </si>
   <si>
     <r>
+      <t xml:space="preserve">Chức vụ </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>*</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Loại người dùng </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>*</t>
+    </r>
+  </si>
+  <si>
+    <r>
       <t xml:space="preserve">Danh sách role </t>
     </r>
     <r>
@@ -155,18 +185,6 @@
   </si>
   <si>
     <t>(8): Nhập danh sách role cách nhau bởi dấu ,</t>
-  </si>
-  <si>
-    <t>VNEID</t>
-  </si>
-  <si>
-    <t>SĐT</t>
-  </si>
-  <si>
-    <t>Mã nhân viên</t>
-  </si>
-  <si>
-    <t>(9)</t>
   </si>
 </sst>
 </file>
@@ -247,7 +265,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -270,12 +288,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -307,16 +334,13 @@
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -600,88 +624,78 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I314"/>
+  <dimension ref="A1:H314"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.25" style="7" customWidth="1"/>
     <col min="2" max="2" width="25.75" style="6" customWidth="1"/>
     <col min="3" max="3" width="28.5" style="6" customWidth="1"/>
     <col min="4" max="5" width="22.75" style="8" customWidth="1"/>
-    <col min="6" max="6" width="18.75" style="10" customWidth="1"/>
+    <col min="6" max="6" width="18.75" style="6" customWidth="1"/>
     <col min="7" max="7" width="19.125" style="6" customWidth="1"/>
     <col min="8" max="8" width="28.5" style="6" customWidth="1"/>
-    <col min="9" max="9" width="9" style="10"/>
-    <col min="10" max="16384" width="9" style="6"/>
+    <col min="9" max="16384" width="9" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
+    <row r="1" spans="1:8" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
-      <c r="H1" s="11"/>
-      <c r="I1" s="11"/>
-    </row>
-    <row r="2" spans="1:9" s="9" customFormat="1" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="12" t="s">
-        <v>16</v>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
+      <c r="H1" s="12"/>
+    </row>
+    <row r="2" spans="1:8" s="9" customFormat="1" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="13" t="s">
+        <v>18</v>
       </c>
-      <c r="B2" s="12"/>
-      <c r="C2" s="12"/>
-      <c r="D2" s="12"/>
-      <c r="E2" s="12"/>
-      <c r="F2" s="12"/>
-      <c r="G2" s="12"/>
-      <c r="H2" s="12"/>
-      <c r="I2" s="12"/>
-    </row>
-    <row r="3" spans="1:9" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="14" t="s">
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="13"/>
+    </row>
+    <row r="3" spans="1:8" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" s="13"/>
+      <c r="C3" s="13"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="13"/>
+      <c r="F3" s="13"/>
+      <c r="G3" s="13"/>
+      <c r="H3" s="13"/>
+    </row>
+    <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="13"/>
+      <c r="B4" s="13"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="13"/>
+      <c r="G4" s="13"/>
+      <c r="H4" s="13"/>
+    </row>
+    <row r="6" spans="1:8" ht="31.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="14"/>
-      <c r="C3" s="14"/>
-      <c r="D3" s="14"/>
-      <c r="E3" s="14"/>
-      <c r="F3" s="14"/>
-      <c r="G3" s="14"/>
-      <c r="H3" s="14"/>
-      <c r="I3" s="14"/>
-    </row>
-    <row r="4" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="12"/>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12"/>
-      <c r="D4" s="12"/>
-      <c r="E4" s="12"/>
-      <c r="F4" s="12"/>
-      <c r="G4" s="12"/>
-      <c r="H4" s="12"/>
-      <c r="I4" s="12"/>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="F5" s="6"/>
-      <c r="I5" s="6"/>
-    </row>
-    <row r="6" spans="1:9" ht="31.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" s="13"/>
-      <c r="C6" s="13"/>
-      <c r="D6" s="13"/>
-      <c r="E6" s="13"/>
-      <c r="F6" s="13"/>
-      <c r="G6" s="13"/>
-      <c r="H6" s="13"/>
-      <c r="I6" s="13"/>
-    </row>
-    <row r="7" spans="1:9" s="2" customFormat="1" ht="87.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="11"/>
+      <c r="C6" s="11"/>
+      <c r="D6" s="11"/>
+      <c r="E6" s="11"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="11"/>
+    </row>
+    <row r="7" spans="1:8" s="2" customFormat="1" ht="87.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
@@ -698,19 +712,16 @@
         <v>10</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
-      <c r="I7" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>0</v>
       </c>
@@ -727,61 +738,58 @@
         <v>4</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
-      <c r="I8" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B9" s="10"/>
       <c r="C9" s="10"/>
       <c r="D9" s="10"/>
       <c r="E9" s="10"/>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B10" s="10"/>
       <c r="C10" s="10"/>
       <c r="D10" s="10"/>
       <c r="E10" s="10"/>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B11" s="10"/>
       <c r="C11" s="10"/>
       <c r="D11" s="10"/>
       <c r="E11" s="10"/>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B12" s="10"/>
       <c r="C12" s="10"/>
       <c r="D12" s="10"/>
       <c r="E12" s="10"/>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B13" s="10"/>
       <c r="C13" s="10"/>
       <c r="D13" s="10"/>
       <c r="E13" s="10"/>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B14" s="10"/>
       <c r="C14" s="10"/>
       <c r="D14" s="10"/>
       <c r="E14" s="10"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B15" s="10"/>
       <c r="C15" s="10"/>
       <c r="D15" s="10"/>
       <c r="E15" s="10"/>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B16" s="10"/>
       <c r="C16" s="10"/>
       <c r="D16" s="10"/>
@@ -2416,11 +2424,11 @@
   </sheetData>
   <autoFilter ref="A7:E8" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="5">
-    <mergeCell ref="A6:I6"/>
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A2:I2"/>
-    <mergeCell ref="A3:I3"/>
-    <mergeCell ref="A4:I4"/>
+    <mergeCell ref="A6:H6"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A4:H4"/>
   </mergeCells>
   <pageMargins left="0.24062500000000001" right="0.22604166666666667" top="0.47499999999999998" bottom="0.35729166666666667" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup scale="70" orientation="landscape" r:id="rId1"/>
